--- a/MMO-Client/excel2json/excel/PanelDefine.xlsx
+++ b/MMO-Client/excel2json/excel/PanelDefine.xlsx
@@ -4,17 +4,30 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24045" windowHeight="12960"/>
+    <workbookView windowHeight="18360"/>
   </bookViews>
   <sheets>
     <sheet name="PanelDefine" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
   <si>
     <t>PanelName</t>
   </si>
@@ -65,12 +78,18 @@
   </si>
   <si>
     <t>Prefabs/UI/CombatPanel</t>
+  </si>
+  <si>
+    <t>PackagePanel</t>
+  </si>
+  <si>
+    <t>Prefabs/UI/Package/PackagePanel</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -1025,7 +1044,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" customHeight="1" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="20.75" style="3" customWidth="1"/>
@@ -1109,6 +1128,14 @@
         <v>16</v>
       </c>
     </row>
+    <row r="10" customHeight="1" spans="1:2">
+      <c r="A10" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
